--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212273</v>
+        <v>120212277</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>96862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342664</v>
+        <v>342897</v>
       </c>
       <c r="R2" t="n">
-        <v>6434900</v>
+        <v>6434891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212277</v>
+        <v>120212273</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +812,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342897</v>
+        <v>342664</v>
       </c>
       <c r="R3" t="n">
-        <v>6434891</v>
+        <v>6434900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,17 +879,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120212277</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>120212273</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212277</v>
+        <v>120212273</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342897</v>
+        <v>342664</v>
       </c>
       <c r="R2" t="n">
-        <v>6434891</v>
+        <v>6434900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,17 +754,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212273</v>
+        <v>120212277</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,42 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342664</v>
+        <v>342897</v>
       </c>
       <c r="R3" t="n">
-        <v>6434900</v>
+        <v>6434891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,11 +894,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212273</v>
+        <v>120212277</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342664</v>
+        <v>342897</v>
       </c>
       <c r="R2" t="n">
-        <v>6434900</v>
+        <v>6434891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,28 +781,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212277</v>
+        <v>120212273</v>
       </c>
       <c r="B3" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +812,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342897</v>
+        <v>342664</v>
       </c>
       <c r="R3" t="n">
-        <v>6434891</v>
+        <v>6434900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,17 +879,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,19 +903,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,956 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120507626</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95517</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>342886</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434884</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120507260</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>342718</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120507538</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>342854</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434881</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120507151</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>342682</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6434904</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120507494</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>342796</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6434878</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120507127</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>342626</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6434922</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120507511</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>342840</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6434904</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120507653</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95517</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>342727</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6434941</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212273</v>
+        <v>120212277</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342664</v>
+        <v>342897</v>
       </c>
       <c r="R2" t="n">
-        <v>6434900</v>
+        <v>6434891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,17 +775,13 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212277</v>
+        <v>120212273</v>
       </c>
       <c r="B3" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +812,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342897</v>
+        <v>342664</v>
       </c>
       <c r="R3" t="n">
-        <v>6434891</v>
+        <v>6434900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,17 +879,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120507626</v>
+        <v>120507538</v>
       </c>
       <c r="B4" t="n">
-        <v>95517</v>
+        <v>57689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,39 +937,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -977,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342886</v>
+        <v>342854</v>
       </c>
       <c r="R4" t="n">
-        <v>6434884</v>
+        <v>6434881</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1009,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
+          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120507260</v>
+        <v>120507151</v>
       </c>
       <c r="B5" t="n">
         <v>96198</v>
@@ -1097,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342718</v>
+        <v>342682</v>
       </c>
       <c r="R5" t="n">
-        <v>6434875</v>
+        <v>6434904</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120507538</v>
+        <v>120507511</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>84228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,31 +1167,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>3518</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,13 +1202,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342854</v>
+        <v>342840</v>
       </c>
       <c r="R6" t="n">
-        <v>6434881</v>
+        <v>6434904</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,7 +1242,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
+          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1251,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120507151</v>
+        <v>120507494</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,35 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342682</v>
+        <v>342796</v>
       </c>
       <c r="R7" t="n">
-        <v>6434904</v>
+        <v>6434878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,6 +1357,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120507494</v>
+        <v>120507653</v>
       </c>
       <c r="B8" t="n">
-        <v>84228</v>
+        <v>95517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,34 +1405,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3518</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342796</v>
+        <v>342727</v>
       </c>
       <c r="R8" t="n">
-        <v>6434878</v>
+        <v>6434941</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
+          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120507127</v>
+        <v>120507626</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>95517</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,43 +1521,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342626</v>
+        <v>342886</v>
       </c>
       <c r="R9" t="n">
-        <v>6434922</v>
+        <v>6434884</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
+          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,6 +1614,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120507511</v>
+        <v>120507260</v>
       </c>
       <c r="B10" t="n">
-        <v>84228</v>
+        <v>96198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,34 +1649,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1683,10 +1685,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342840</v>
+        <v>342718</v>
       </c>
       <c r="R10" t="n">
-        <v>6434904</v>
+        <v>6434875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,11 +1721,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120507653</v>
+        <v>120507127</v>
       </c>
       <c r="B11" t="n">
-        <v>95517</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,39 +1760,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1803,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>342727</v>
+        <v>342626</v>
       </c>
       <c r="R11" t="n">
-        <v>6434941</v>
+        <v>6434922</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1843,7 +1844,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
+          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,7 +1853,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212277</v>
+        <v>120212273</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342897</v>
+        <v>342664</v>
       </c>
       <c r="R2" t="n">
-        <v>6434891</v>
+        <v>6434900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,17 +754,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212273</v>
+        <v>120212277</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,42 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342664</v>
+        <v>342897</v>
       </c>
       <c r="R3" t="n">
-        <v>6434900</v>
+        <v>6434891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,17 +896,13 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120507538</v>
+        <v>120507127</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,8 +960,16 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -969,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342854</v>
+        <v>342626</v>
       </c>
       <c r="R4" t="n">
-        <v>6434881</v>
+        <v>6434922</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
+          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1151,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120507511</v>
+        <v>120507626</v>
       </c>
       <c r="B6" t="n">
-        <v>84228</v>
+        <v>95517</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,34 +1175,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3518</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342840</v>
+        <v>342886</v>
       </c>
       <c r="R6" t="n">
-        <v>6434904</v>
+        <v>6434884</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,7 +1255,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
+          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120507494</v>
+        <v>120507653</v>
       </c>
       <c r="B7" t="n">
-        <v>84228</v>
+        <v>95517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1299,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3518</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342796</v>
+        <v>342727</v>
       </c>
       <c r="R7" t="n">
-        <v>6434878</v>
+        <v>6434941</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,7 +1375,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
+          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120507653</v>
+        <v>120507260</v>
       </c>
       <c r="B8" t="n">
-        <v>95517</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,26 +1419,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342727</v>
+        <v>342718</v>
       </c>
       <c r="R8" t="n">
-        <v>6434941</v>
+        <v>6434875</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1477,11 +1491,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120507626</v>
+        <v>120507538</v>
       </c>
       <c r="B9" t="n">
-        <v>95517</v>
+        <v>57689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,39 +1534,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2590</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1565,13 +1566,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342886</v>
+        <v>342854</v>
       </c>
       <c r="R9" t="n">
-        <v>6434884</v>
+        <v>6434881</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,7 +1606,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
+          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,7 +1615,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120507260</v>
+        <v>120507511</v>
       </c>
       <c r="B10" t="n">
-        <v>96198</v>
+        <v>84228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,35 +1649,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>3518</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1685,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342718</v>
+        <v>342840</v>
       </c>
       <c r="R10" t="n">
-        <v>6434875</v>
+        <v>6434904</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,6 +1720,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120507127</v>
+        <v>120507494</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>84228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,43 +1764,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3518</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1804,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>342626</v>
+        <v>342796</v>
       </c>
       <c r="R11" t="n">
-        <v>6434922</v>
+        <v>6434878</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1844,7 +1843,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
+          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,6 +1852,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -2092,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120810554</v>
+        <v>120810549</v>
       </c>
       <c r="B14" t="n">
-        <v>56560</v>
+        <v>58028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,42 +2108,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Funtamosse 7, Vg</t>
+          <t>S Funtamosse 4, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>342942</v>
+        <v>342682</v>
       </c>
       <c r="R14" t="n">
-        <v>6434814</v>
+        <v>6434894</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2175,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,12 +2189,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Både äldre och färskare spillning.</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120810549</v>
+        <v>120810541</v>
       </c>
       <c r="B15" t="n">
-        <v>58025</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,20 +2228,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2257,22 +2256,18 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S Funtamosse 4, Vg</t>
+          <t>S Funtamosse 1, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>342682</v>
+        <v>342752</v>
       </c>
       <c r="R15" t="n">
-        <v>6434894</v>
+        <v>6434930</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2304,7 +2299,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2309,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flög hit och dit och skrek under de timmar jag var på plats.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120810552</v>
+        <v>120810554</v>
       </c>
       <c r="B16" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,20 +2379,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>S Funtamosse 6, Vg</t>
+          <t>S Funtamosse 7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>342940</v>
+        <v>342942</v>
       </c>
       <c r="R16" t="n">
-        <v>6434815</v>
+        <v>6434814</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera högar.</t>
+          <t>Både äldre och färskare spillning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,10 +2466,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120810541</v>
+        <v>120810552</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>56563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,46 +2478,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S Funtamosse 1, Vg</t>
+          <t>S Funtamosse 6, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>342752</v>
+        <v>342940</v>
       </c>
       <c r="R17" t="n">
-        <v>6434930</v>
+        <v>6434815</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flög hit och dit och skrek under de timmar jag var på plats.</t>
+          <t>Flera högar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,7 +2594,7 @@
         <v>120810569</v>
       </c>
       <c r="B18" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>120810569</v>
       </c>
       <c r="B18" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>120810569</v>
       </c>
       <c r="B18" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>120810569</v>
       </c>
       <c r="B18" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -2594,7 +2594,7 @@
         <v>120810569</v>
       </c>
       <c r="B18" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120212277</v>
+        <v>120507151</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Funtamosse, Vg</t>
+          <t>Funtamosse, söder om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342897</v>
+        <v>342682</v>
       </c>
       <c r="R2" t="n">
-        <v>6434891</v>
+        <v>6434904</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,69 +773,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120212273</v>
+        <v>120507243</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hålanda skog, Vg</t>
+          <t>Funtamosse, söder om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342664</v>
+        <v>342688</v>
       </c>
       <c r="R3" t="n">
-        <v>6434900</v>
+        <v>6434881</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,33 +876,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120507260</v>
+        <v>120507253</v>
       </c>
       <c r="B4" t="n">
-        <v>96317</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342718</v>
+        <v>342685</v>
       </c>
       <c r="R4" t="n">
-        <v>6434875</v>
+        <v>6434883</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1036,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120507494</v>
+        <v>120507260</v>
       </c>
       <c r="B5" t="n">
-        <v>84285</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,34 +1016,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3518</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>342796</v>
+        <v>342718</v>
       </c>
       <c r="R5" t="n">
-        <v>6434878</v>
+        <v>6434875</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,11 +1088,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,55 +1115,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120507127</v>
+        <v>120507626</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1211,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>342626</v>
+        <v>342886</v>
       </c>
       <c r="R6" t="n">
-        <v>6434922</v>
+        <v>6434884</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,7 +1206,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
+          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,6 +1215,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,15 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120507511</v>
+        <v>120507653</v>
       </c>
       <c r="B7" t="n">
-        <v>84285</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,34 +1245,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3518</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>342840</v>
+        <v>342727</v>
       </c>
       <c r="R7" t="n">
-        <v>6434904</v>
+        <v>6434941</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,7 +1321,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
+          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,15 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120507151</v>
+        <v>120212304</v>
       </c>
       <c r="B8" t="n">
-        <v>96317</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,46 +1360,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Funtamosse, söder om, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>342682</v>
+        <v>342700</v>
       </c>
       <c r="R8" t="n">
-        <v>6434904</v>
+        <v>6434862</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1479,12 +1422,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,27 +1453,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120507538</v>
+        <v>120212290</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,45 +1476,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>3518</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Funtamosse, söder om, Vg</t>
+          <t>Hålanda skog 2, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>342854</v>
+        <v>342745</v>
       </c>
       <c r="R9" t="n">
-        <v>6434881</v>
+        <v>6434858</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,17 +1533,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,33 +1557,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120507653</v>
+        <v>120507494</v>
       </c>
       <c r="B10" t="n">
-        <v>95636</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,35 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>3518</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1679,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>342727</v>
+        <v>342796</v>
       </c>
       <c r="R10" t="n">
-        <v>6434941</v>
+        <v>6434878</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växte på en låga i våtmarkskanten vid Funtamosses södra kant. Några 10-tals meter NNO om ett överhäng där det växte svartbräken.</t>
+          <t>Växte i mossmatta bland knappt medelgrova-medelgrova granar. Stod i två grupperingar med 4 m mellanrum.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,15 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120507626</v>
+        <v>120507511</v>
       </c>
       <c r="B11" t="n">
-        <v>95636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,39 +1701,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>3518</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1803,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>342886</v>
+        <v>342840</v>
       </c>
       <c r="R11" t="n">
-        <v>6434884</v>
+        <v>6434904</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1843,7 +1776,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte på samma låga som fyra gullnavlingar. Lågan, som troligen var en granlåga, låg uppallad av en sten så att den hängde i luften. Lågan låg nedanför en bergbrant, nära surdraget i öster.</t>
+          <t>Växte i mossmatta i knappt medelgrov granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,37 +1804,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120642673</v>
+        <v>120212273</v>
       </c>
       <c r="B12" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,14 +1839,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hålanda, Vg</t>
+          <t>Hålanda skog, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>342858</v>
+        <v>342664</v>
       </c>
       <c r="R12" t="n">
-        <v>6434924</v>
+        <v>6434900</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,9 +1876,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med spillkråkehack i en stubbe och en torraka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,27 +1908,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120723691</v>
+        <v>120507127</v>
       </c>
       <c r="B13" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1931,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2016,22 +1954,30 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hålanda, Vg</t>
+          <t>Funtamosse, söder om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>342858</v>
+        <v>342626</v>
       </c>
       <c r="R13" t="n">
-        <v>6434924</v>
+        <v>6434922</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,17 +2001,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tjäderspillning</t>
+          <t>Sågs först flyga över ett äldre hygge med frötallar mot sydost. Satte sig i en tall i den västra kanten på den avverkningsanmälda ytan. Hördes sedan vid flera tillfällen under mitt besök.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,27 +2026,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120810549</v>
+        <v>120507226</v>
       </c>
       <c r="B14" t="n">
-        <v>58028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,16 +2049,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2125,32 +2066,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Funtamosse 4, Vg</t>
+          <t>Funtamosse, söder om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>342682</v>
+        <v>342652</v>
       </c>
       <c r="R14" t="n">
-        <v>6434894</v>
+        <v>6434895</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2174,22 +2111,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 st granhögstubbar med spillkråkehack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,12 +2136,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,16 +2151,11 @@
         <v>120810541</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2341,15 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120810554</v>
+        <v>120723691</v>
       </c>
       <c r="B16" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,28 +2296,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>S Funtamosse 7, Vg</t>
+          <t>Hålanda, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>342942</v>
+        <v>342858</v>
       </c>
       <c r="R16" t="n">
-        <v>6434814</v>
+        <v>6434924</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2419,27 +2341,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Både äldre och färskare spillning.</t>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,12 +2366,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2469,12 +2381,7 @@
         <v>120810552</v>
       </c>
       <c r="B17" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2591,15 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120810569</v>
+        <v>120810554</v>
       </c>
       <c r="B18" t="n">
-        <v>105209</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,38 +2509,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>S Funtamosse 13, Vg</t>
+          <t>S Funtamosse 7, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>342702</v>
+        <v>342942</v>
       </c>
       <c r="R18" t="n">
-        <v>6434941</v>
+        <v>6434814</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2670,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2680,12 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Stöd i artbestämning via Facebook-gruppen Svensk Botanik.</t>
+          <t>Både äldre och färskare spillning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2694,7 +2600,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2710,6 +2615,685 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120507538</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>342854</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6434881</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I sydöstra hörnet av den avverkningsanmälda ytan.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120642588</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hålanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>342858</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6434924</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120810549</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>S Funtamosse 4, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>342682</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6434894</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120507700</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Funtamosse, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>342851</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6434950</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera hålrader av björksplintborren på en björkhögstubbe en bit ut i Funtamosse.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120810569</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>S Funtamosse 13, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>342702</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6434941</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stöd i artbestämning via Facebook-gruppen Svensk Botanik.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120212277</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>342897</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6434891</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41294-2024 artfynd.xlsx
+++ b/artfynd/A 41294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507253</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507626</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120212304</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120212290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507494</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507511</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120212273</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507127</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507226</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2265,6 +2335,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120810541</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2375,6 +2450,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723691</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2495,6 +2575,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120810552</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2615,6 +2700,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120810554</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2725,6 +2815,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507538</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2826,6 +2921,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120642588</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2945,6 +3045,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120810549</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3057,6 +3162,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507700</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3174,6 +3284,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120810569</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3294,8 +3409,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120212277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>